--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2021_antofagasta.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:21</t>
+    <t xml:space="preserve">2026-09-24 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>-0.03</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.22</v>
@@ -762,10 +762,10 @@
         <v>0.12</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="12">
@@ -785,7 +785,7 @@
         <v>-0.09</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="14">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2021_antofagasta.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:11</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2021_antofagasta.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
